--- a/descriptive tables/acute_nepal.xlsx
+++ b/descriptive tables/acute_nepal.xlsx
@@ -301,7 +301,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -320,10 +320,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>6.17</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -331,164 +331,175 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.73</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>218</v>
+        <v>12</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>39.56</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>11</v>
+        <v>697</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>2</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.36</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.73</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.73</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>3.09</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>3.81</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.91</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>5.26</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>8.35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>1.27</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>7.8</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
         <v>96</v>
       </c>
-      <c r="B17" s="0" t="n">
-        <v>93</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>16.88</v>
+      <c r="B18" s="0" t="n">
+        <v>348</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>21.08</v>
       </c>
     </row>
   </sheetData>
